--- a/FYP/Matrices/Refined Research Gap Analysis Matrix v6.xlsx
+++ b/FYP/Matrices/Refined Research Gap Analysis Matrix v6.xlsx
@@ -649,21 +649,22 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="85" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Version 6.0 | Refined against all 59 literature reviews | Sentiment out of scope (supervisor decision 20 Sep 2026, Final) | Context: Colombo Stock Exchange</t>
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="3" customHeight="1"/>
+    <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>THESIS ARCHITECTURE HIERARCHY</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="12" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Level / Category</t>
@@ -685,7 +686,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="88" customHeight="1">
+    <row r="6" ht="122" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>MAIN RESEARCH GAP</t>
@@ -817,14 +818,15 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="12" customHeight="1"/>
+    <row r="13" ht="24" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>WHAT CHANGED IN V5, AND WHY</t>
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="12" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Change</t>
@@ -842,7 +844,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr"/>
     </row>
-    <row r="15" ht="96" customHeight="1">
+    <row r="15" ht="110" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Main gap reformulated from 'weights are fixed' to 'there is no quantity that could be weighted'</t>
@@ -878,7 +880,7 @@
       </c>
       <c r="D16" s="8" t="inlineStr"/>
     </row>
-    <row r="17" ht="96" customHeight="1">
+    <row r="17" ht="98" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Automate Strategy Finding demoted from competitor to Baseline 2</t>
@@ -932,7 +934,7 @@
       </c>
       <c r="D19" s="8" t="inlineStr"/>
     </row>
-    <row r="20" ht="96" customHeight="1">
+    <row r="20" ht="98" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Conditioning set resolved; C_i,t redefined; abstention added</t>
@@ -950,7 +952,7 @@
       </c>
       <c r="D20" s="8" t="inlineStr"/>
     </row>
-    <row r="21" ht="96" customHeight="1">
+    <row r="21" ht="98" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Four-agent pool confirmed, macro agent rejected on CSE evidence</t>
@@ -968,7 +970,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr"/>
     </row>
-    <row r="22" ht="96" customHeight="1">
+    <row r="22" ht="122" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
           <t>CSE data blocker reframed rather than resolved</t>
@@ -986,7 +988,7 @@
       </c>
       <c r="D22" s="8" t="inlineStr"/>
     </row>
-    <row r="23" ht="96" customHeight="1">
+    <row r="23" ht="110" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
           <t>CORRECTION carried from the reviews</t>
@@ -1004,14 +1006,15 @@
       </c>
       <c r="D23" s="8" t="inlineStr"/>
     </row>
-    <row r="25">
+    <row r="24" customHeight="1"/>
+    <row r="25" ht="24" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
           <t>OPEN ITEMS - THREE CLOSED SINCE V4</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="85" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
           <t>CLOSED</t>
@@ -1025,7 +1028,7 @@
       <c r="C26" s="10" t="n"/>
       <c r="D26" s="11" t="n"/>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="73" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
         <is>
           <t>CLOSED</t>
@@ -1039,7 +1042,7 @@
       <c r="C27" s="10" t="n"/>
       <c r="D27" s="11" t="n"/>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="85" customHeight="1">
       <c r="A28" s="12" t="inlineStr">
         <is>
           <t>PARTLY CLOSED</t>
@@ -1053,7 +1056,7 @@
       <c r="C28" s="10" t="n"/>
       <c r="D28" s="11" t="n"/>
     </row>
-    <row r="29" ht="56" customHeight="1">
+    <row r="29" ht="146" customHeight="1">
       <c r="A29" s="13" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1061,13 +1064,13 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>3. CSE per-counter data depth. Reframed, not resolved. The index track is secure at ten years daily; the per-counter track is roughly February 2025 to February 2026. The cross-sectional pooling reframe makes that workable at a short lookback, so the question is now how many counters clear a liquidity screen rather than how many years exist.</t>
+          <t>3. CSE per-counter data depth. [CORRECTED 18 OCTOBER 2026] LARGELY CLOSED. The February 2025 to February 2026 figure was the Chindara archive. The project's own extraction holds 2012-01-02 to 2026-10-02, about 14.75 years, 323 securities, roughly 829,070 security-day observations. The question of how many counters clear a liquidity screen stands, and a new one replaces the old depth question: the series is not adjusted for corporate actions and the adjusted series has to be built before the depth is usable.</t>
         </is>
       </c>
       <c r="C29" s="10" t="n"/>
       <c r="D29" s="11" t="n"/>
     </row>
-    <row r="30" ht="56" customHeight="1">
+    <row r="30" ht="61" customHeight="1">
       <c r="A30" s="13" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1081,7 +1084,7 @@
       <c r="C30" s="10" t="n"/>
       <c r="D30" s="11" t="n"/>
     </row>
-    <row r="31" ht="56" customHeight="1">
+    <row r="31" ht="85" customHeight="1">
       <c r="A31" s="13" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1095,7 +1098,7 @@
       <c r="C31" s="10" t="n"/>
       <c r="D31" s="11" t="n"/>
     </row>
-    <row r="32" ht="56" customHeight="1">
+    <row r="32" ht="61" customHeight="1">
       <c r="A32" s="13" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -1109,7 +1112,7 @@
       <c r="C32" s="10" t="n"/>
       <c r="D32" s="11" t="n"/>
     </row>
-    <row r="33" ht="56" customHeight="1">
+    <row r="33" ht="110" customHeight="1">
       <c r="A33" s="12" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -1123,7 +1126,7 @@
       <c r="C33" s="10" t="n"/>
       <c r="D33" s="11" t="n"/>
     </row>
-    <row r="34" ht="56" customHeight="1">
+    <row r="34" ht="73" customHeight="1">
       <c r="A34" s="12" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -1137,14 +1140,15 @@
       <c r="C34" s="10" t="n"/>
       <c r="D34" s="11" t="n"/>
     </row>
-    <row r="36">
+    <row r="35" customHeight="1"/>
+    <row r="36" ht="24" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
           <t>WHAT CHANGED IN V6, AND WHY</t>
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="12" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Change</t>
@@ -1461,7 +1465,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Per-counter CSE daily price and turnover for L_t; ASPI and S&amp;P SL20 daily closes across the three regimes for P_t and V_t; A_F's retrieval output over CSE annual reports with a publication-date field on every document; and per-agent confidence, which is now specified rather than open (see the Conditioning Set sheet). The cross-sectional reframe changes what depth is needed: at a 30-day lookback with roughly 240 days and a couple of hundred tradable counters the sequence count reaches 40,000 to 50,000, so the sample is the cross-section rather than the history.</t>
+          <t>Per-counter CSE daily price and turnover for L_t; ASPI and S&amp;P SL20 daily closes across the three regimes for P_t and V_t; A_F's retrieval output over CSE annual reports with a publication-date field on every document; and per-agent confidence, which is now specified rather than open (see the Conditioning Set sheet). [CORRECTED 18 OCTOBER 2026] THE DATA-DEPTH POSITION HAS CHANGED AND THIS CELL PREVIOUSLY UNDERSTATED IT BY ROUGHLY A FACTOR OF NINE. The 374-day, February 2025 to February 2026 figure was the Chindara archive and is superseded. The project's own extraction holds 2012-01-02 to 2026-10-02, about 14.75 years, 323 securities and roughly 829,070 security-day observations, with turnover and trade count. At a 30-day lookback that is on the order of 820,000 sequences rather than 40,000 to 50,000. Coverage is uneven, so quote the envelope carefully: the median security carries about 2,935 trading days and the tenth percentile about 1,081. The cross-sectional reframe is therefore a convenience rather than a necessity, and all three regime episodes sit inside the sample. ONE NEW PRECONDITION: the series is not adjusted for corporate actions (a JKH split appears as a -90% return), so the adjusted series has to be built before any of this depth is usable.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -1472,18 +1476,18 @@
       <c r="K2" s="2" t="inlineStr">
         <is>
           <t>Three weighting schemes, then each state input ablated alone. The Graph-RAG paper supplies the discipline requirement that protects this: its fatal flaw is that the proposed system got both the graph and the agent scaffolding while the baseline got neither, so Baseline 2 has to be identical to the proposed system in every respect except the weighting function, and the ablations move one input at a time. Pre-registered diagnostics: weight-distribution ENTROPY over time, plus a cross-play check. A_F on/off inside the full framework is now required rather than optional, on the precedent that a text channel bolted onto a working structured pipeline cost 10.36 points with nothing able to notice. Report behavioural-fidelity metrics beside returns, equalise trade counts before comparing, report exposure time, holding period and turnover, and commit to dispersion and a paired significance test before seeing numbers.
-PRE-REGISTRATION, ADDED IN V6. Before the first run, record the margin over equal weights and the paired significance test that would count as the state-conditioned weighting having earned its place, together with the direction the forecast combination literature predicts. Both outcomes are reportable: the review states that comprehensive quantitative guidance on when estimated weights beat fixed ones does not yet exist in that literature, so a pre-registered answer on a thin frontier market is a contribution even if the answer is that equal weights win. Record also the absence of a pairwise interaction term as a deliberate choice rather than an oversight, since with four agents an interaction form is ten parameters against four on roughly 374 days, and the combination literature tried that first and moved away from it.</t>
+PRE-REGISTRATION, ADDED IN V6. Before the first run, record the margin over equal weights and the paired significance test that would count as the state-conditioned weighting having earned its place, together with the direction the forecast combination literature predicts. Both outcomes are reportable: the review states that comprehensive quantitative guidance on when estimated weights beat fixed ones does not yet exist in that literature, so a pre-registered answer on a thin frontier market is a contribution even if the answer is that equal weights win. Record also the absence of a pairwise interaction term as a deliberate choice rather than an oversight, since with four agents an interaction form is ten parameters against four. [CORRECTED 18 OCTOBER 2026] The denominator is roughly 3,400 trading days per counter, not the 374 previously recorded here, so ten parameters is no longer self-evidently too many and the omission has to rest on the instability of covariance estimates, which is what Bates and Granger and the authors after them actually argue, rather than on a parameter count.</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Medium. The orchestrator is small and cheap relative to the agents beneath it, and the capacity constraint argues for keeping it small anyway. The binding constraints have changed since v4: agent confidence is no longer the open problem it was, and the cross-sectional reframe has softened the data-depth constraint, so the sharpest remaining constraint is whether a February 2025 to February 2026 series contains enough regime variation for a state-conditioned weighting to have anything to learn from.</t>
+          <t>Medium. The orchestrator is small and cheap relative to the agents beneath it, and the capacity constraint argues for keeping it small anyway. The binding constraints have changed since v4: agent confidence is no longer the open problem it was, and the cross-sectional reframe has softened the data-depth constraint, so the sharpest remaining constraint is no longer history length. [CORRECTED 18 OCTOBER 2026] The per-counter track is 2012-01-02 to 2026-10-02, not February 2025 to February 2026, and it contains the Easter attacks, COVID and the 2022 crisis, so regime variation is present rather than doubtful. The two binding constraints now are that the series is unadjusted for corporate actions and must be corrected first, and that per-counter coverage is uneven, so eligibility is a per-counter test rather than a blanket one.</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
           <t>The entropy collapse risk stands and the pre-registered diagnostic stands with it. A second risk is now better defined: with A_F usable less than half the time, the orchestrator may learn to zero it permanently rather than conditionally, in which case the heterogeneity claim survives on paper while the system behaves as a three-agent one, and the weight trajectory around reporting dates is the natural test of whether the mechanism is conditional or merely selective. Third, the regularisation sign-flip observed on a larger dataset than the CSE offers means the orchestrator's own stability has to be swept and reported rather than tuned once. Fourth, the Agentic Trading cutoff means this gap statement has a shelf life and should be re-checked before submission.
-FIFTH, AND ADDED IN V6, THE FORECAST COMBINATION PUZZLE IS THE FIELD'S STANDING PRIOR AGAINST THIS DESIGN AND IT BELONGS IN THE WRITE-UP BEFORE THE RESULTS RATHER THAN AFTER THEM. Elliott bounds the available gain from optimal over equal weights as usually too small to pay for the estimation; Claeskens et al. show estimated weights can introduce bias into a combination of unbiased components and inflate variance past the fixed-weight case; and the probabilistic side reproduces the pattern independently. Everything that literature says about estimation error swamping the gains is worse in my setting, not better, because my components are themselves estimated on short, illiquid and intermittently traded series. The review's own two practical guidelines cut in opposite directions here: with limited historical data it recommends the simple average or weights that ignore covariances, which my roughly 374 trading days per counter argues for, while it also holds that structural change affects sophisticated schemes more than the simple average and that changing weights are a legitimate response to it, which is the entire premise of conditioning on state. Which effect dominates on CSE data is the empirical question, and a failure to beat equal weights is the expected outcome under the field's prior rather than a surprise.</t>
+FIFTH, AND ADDED IN V6, THE FORECAST COMBINATION PUZZLE IS THE FIELD'S STANDING PRIOR AGAINST THIS DESIGN AND IT BELONGS IN THE WRITE-UP BEFORE THE RESULTS RATHER THAN AFTER THEM. Elliott bounds the available gain from optimal over equal weights as usually too small to pay for the estimation; Claeskens et al. show estimated weights can introduce bias into a combination of unbiased components and inflate variance past the fixed-weight case; and the probabilistic side reproduces the pattern independently. Everything that literature says about estimation error swamping the gains is worse in my setting, not better, because my components are themselves estimated on short, illiquid and intermittently traded series. The review's own two practical guidelines cut in opposite directions here: with limited historical data it recommends the simple average or weights that ignore covariances, which [CORRECTED 18 OCTOBER 2026] was written against a 374-day archive and is weaker than it reads, since the per-counter track is roughly 3,400 trading days; the guideline still bites because the components are themselves estimated on illiquid, intermittently traded series and calendar depth is not effective sample size, but equal weights is no longer favoured by data length alone. The review also holds that structural change affects sophisticated schemes more than the simple average and that changing weights are a legitimate response to it, which is the entire premise of conditioning on state. Which effect dominates on CSE data is the empirical question, and a failure to beat equal weights is the expected outcome under the field's prior rather than a surprise.</t>
         </is>
       </c>
       <c r="N2" s="17" t="inlineStr">
